--- a/monitoring_forms/013_process_data_monitoring_report_form--monitoring_forms.xlsx
+++ b/monitoring_forms/013_process_data_monitoring_report_form--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Process Data</t>
+          <t>Process Data Monitoring</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -669,14 +669,14 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Review Date</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Review Time</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Report Type</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sub Category</t>
+          <t>Report Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Report Type</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Report Date</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,20 +824,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,243 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Report Type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Review Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Review Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Report Date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1160,7 +930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_3_choices</t>
+          <t>process_data_monitoring_report_form_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +947,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_3_choices</t>
+          <t>process_data_monitoring_report_form_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +964,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_10_choices</t>
+          <t>process_data_monitoring_report_form_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +981,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_10_choices</t>
+          <t>process_data_monitoring_report_form_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +998,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_11_choices</t>
+          <t>process_data_monitoring_report_form_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1015,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_11_choices</t>
+          <t>process_data_monitoring_report_form_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1032,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_12_choices</t>
+          <t>process_data_monitoring_report_form_9_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1049,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_12_choices</t>
+          <t>process_data_monitoring_report_form_9_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1066,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_18_choices</t>
+          <t>process_data_monitoring_report_form_10_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1083,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>process_data_monitoring_report_form_18_choices</t>
+          <t>process_data_monitoring_report_form_10_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,244 +1092,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>process_data_monitoring_report_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
